--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -17379,27 +17379,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-19T17:10:00Z</t>
+          <t>2026-08-20T00:40:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17409,17 +17409,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17428,7 +17428,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17442,26 +17442,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>50.5</v>
+        <v>31.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>45.2</v>
+        <v>53.2</v>
       </c>
       <c r="R63" t="n">
-        <v>24.8</v>
+        <v>38.7</v>
       </c>
       <c r="S63" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T63" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U63" t="n">
-        <v>12</v>
+        <v>42.3</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
@@ -17527,124 +17527,124 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 7/25, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.5% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>100.7432</t>
+          <t>100.1834</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4746</t>
+          <t>0.3848</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3379</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>42.04</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1776</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.4995</t>
+          <t>0.4237</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.2089</t>
+          <t>0.1831</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr"/>
       <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -17655,27 +17655,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19T22:35:00Z</t>
+          <t>2026-08-19T17:10:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -17685,17 +17685,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -17718,26 +17718,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>48</v>
+        <v>50.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>48.6</v>
+        <v>45.2</v>
       </c>
       <c r="R64" t="n">
-        <v>32.1</v>
+        <v>24.8</v>
       </c>
       <c r="S64" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T64" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U64" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -17793,12 +17793,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -17808,119 +17808,119 @@
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 19.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>11.46</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>45.98</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>100.3995</t>
+          <t>100.7432</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.4746</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.2149</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3264</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>37.98</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1776</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>32.92</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.4218</t>
+          <t>0.4995</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2089</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr"/>
       <c r="BH64" t="inlineStr"/>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -17931,27 +17931,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19T22:40:00Z</t>
+          <t>2026-08-19T22:35:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -17961,17 +17961,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -17994,26 +17994,26 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q65" t="n">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="R65" t="n">
-        <v>27.6</v>
+        <v>32.1</v>
       </c>
       <c r="S65" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T65" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U65" t="n">
-        <v>45.9</v>
+        <v>16.6</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -18069,134 +18069,134 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>11.46</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>90.05</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>100.1652</t>
+          <t>100.3995</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.4248</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.2149</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.3207</t>
+          <t>0.3264</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>73.65</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>34.19</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.2099</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4218</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.2013</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr"/>
       <c r="BH65" t="inlineStr"/>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18207,27 +18207,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20T00:40:00Z</t>
+          <t>2026-08-19T22:40:00Z</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -18237,17 +18237,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18256,7 +18256,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -18270,26 +18270,26 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>31.1</v>
+        <v>45</v>
       </c>
       <c r="Q66" t="n">
-        <v>53.2</v>
+        <v>50.1</v>
       </c>
       <c r="R66" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S66" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T66" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U66" t="n">
-        <v>37.8</v>
+        <v>45.9</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -18345,134 +18345,134 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.5% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>90.05</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>100.1834</t>
+          <t>100.1652</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.3848</t>
+          <t>0.4248</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.3207</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>73.65</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>42.04</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>34.19</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.2099</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.4237</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.1831</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr"/>
       <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -27793,7 +27793,7 @@
         <v>75</v>
       </c>
       <c r="U101" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -27864,7 +27864,7 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
@@ -36267,27 +36267,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>681198</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TJ Rumfield</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-20T00:40:00Z</t>
+          <t>2026-08-19T22:40:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -36297,26 +36297,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Roki Sasaki</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>808963</t>
+          <t>669461</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -36330,26 +36330,26 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P133" t="n">
-        <v>11.2</v>
+        <v>31.3</v>
       </c>
       <c r="Q133" t="n">
-        <v>54.9</v>
+        <v>51.8</v>
       </c>
       <c r="R133" t="n">
-        <v>38.7</v>
+        <v>39.3</v>
       </c>
       <c r="S133" t="n">
-        <v>90.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T133" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U133" t="n">
-        <v>21.1</v>
+        <v>43.2</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -36388,7 +36388,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr"/>
@@ -36405,27 +36405,27 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 4/14, 1 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.5% barrel, 16.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -36435,104 +36435,104 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>95.975</t>
+          <t>99.6624</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>0.3812</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.2953</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.0962</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.4237</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.1831</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr"/>
       <c r="BH133" t="inlineStr"/>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -36543,27 +36543,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-19T22:40:00Z</t>
+          <t>2026-08-20T00:40:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -36573,22 +36573,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>669461</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -36606,26 +36606,26 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>31.3</v>
+        <v>14.2</v>
       </c>
       <c r="Q134" t="n">
-        <v>51.8</v>
+        <v>54.9</v>
       </c>
       <c r="R134" t="n">
-        <v>39.3</v>
+        <v>38.7</v>
       </c>
       <c r="S134" t="n">
-        <v>40.2</v>
+        <v>88.7</v>
       </c>
       <c r="T134" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U134" t="n">
-        <v>43.2</v>
+        <v>3.4</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -36686,22 +36686,22 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 1 HR</t>
+          <t>Last 7 games: 4/28, 0 HR</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.5% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -36711,104 +36711,104 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>99.6624</t>
+          <t>96.5517</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.3812</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.1329</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.2953</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.0962</t>
+          <t>0.1802</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.4461</t>
+          <t>0.4237</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1831</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr"/>
       <c r="BH134" t="inlineStr"/>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -36819,27 +36819,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>805808</t>
+          <t>681198</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Kevin McGonigle</t>
+          <t>TJ Rumfield</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-19T16:35:00Z</t>
+          <t>2026-08-20T00:40:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -36849,17 +36849,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Roki Sasaki</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>808963</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -36886,22 +36886,22 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>31.4</v>
+        <v>11.2</v>
       </c>
       <c r="Q135" t="n">
-        <v>30.9</v>
+        <v>54.9</v>
       </c>
       <c r="R135" t="n">
-        <v>24.3</v>
+        <v>38.7</v>
       </c>
       <c r="S135" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T135" t="n">
         <v>80</v>
       </c>
       <c r="U135" t="n">
-        <v>27.1</v>
+        <v>19.5</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -36957,87 +36957,87 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 1 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.5% barrel, 16.5 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>98.2363</t>
+          <t>95.975</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -37047,44 +37047,44 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.4237</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1831</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr"/>
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
@@ -37095,27 +37095,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>805808</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Kevin McGonigle</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-19T17:40:00Z</t>
+          <t>2026-08-19T16:35:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -37125,17 +37125,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>AJ Smith-Shawver</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>700363</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -37158,27 +37158,27 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Projected Lineup, Pitcher Vulnerable</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="Q136" t="n">
-        <v>74.3</v>
+        <v>30.9</v>
       </c>
       <c r="R136" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S136" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="T136" t="n">
+        <v>80</v>
+      </c>
+      <c r="U136" t="n">
         <v>27.1</v>
       </c>
-      <c r="S136" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="T136" t="n">
-        <v>50</v>
-      </c>
-      <c r="U136" t="n">
-        <v>22.4</v>
-      </c>
       <c r="V136" t="inlineStr">
         <is>
           <t>No</t>
@@ -37191,7 +37191,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -37233,134 +37233,134 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 14.6% barrel, 1.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>100.0963</t>
+          <t>98.2363</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.423</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.5163</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.2185</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr"/>
       <c r="BH136" t="inlineStr"/>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -37371,27 +37371,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-19T17:40:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -37401,12 +37401,24 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>AJ Smith-Shawver</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>700363</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L137" t="n">
         <v>43.4</v>
       </c>
@@ -37422,26 +37434,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Pitcher Vulnerable</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>54</v>
+        <v>31.1</v>
       </c>
       <c r="Q137" t="n">
-        <v>41.2</v>
+        <v>74.3</v>
       </c>
       <c r="R137" t="n">
-        <v>23.2</v>
+        <v>27.1</v>
       </c>
       <c r="S137" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T137" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U137" t="n">
-        <v>1.6</v>
+        <v>22.4</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -37455,7 +37467,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -37480,7 +37492,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -37497,12 +37509,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -37512,95 +37524,119 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/23, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 14.6% barrel, 1.2 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>92.04</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>102.6127</t>
+          <t>100.0963</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.1969</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.281</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.2024</t>
-        </is>
-      </c>
-      <c r="BA137" t="inlineStr"/>
-      <c r="BB137" t="inlineStr"/>
-      <c r="BC137" t="inlineStr"/>
-      <c r="BD137" t="inlineStr"/>
-      <c r="BE137" t="inlineStr"/>
-      <c r="BF137" t="inlineStr"/>
+          <t>0.143</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>14.56</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>91.82</t>
+        </is>
+      </c>
+      <c r="BD137" t="inlineStr">
+        <is>
+          <t>0.5163</t>
+        </is>
+      </c>
+      <c r="BE137" t="inlineStr">
+        <is>
+          <t>0.2185</t>
+        </is>
+      </c>
+      <c r="BF137" t="inlineStr">
+        <is>
+          <t>30.71</t>
+        </is>
+      </c>
       <c r="BG137" t="inlineStr"/>
       <c r="BH137" t="inlineStr"/>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -37611,27 +37647,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-20T00:40:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -37641,26 +37677,14 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Roki Sasaki</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>808963</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -37674,26 +37698,26 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P138" t="n">
-        <v>14.2</v>
+        <v>54</v>
       </c>
       <c r="Q138" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="R138" t="n">
-        <v>38.7</v>
+        <v>23.2</v>
       </c>
       <c r="S138" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T138" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -37707,7 +37731,7 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -37732,7 +37756,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr"/>
@@ -37754,7 +37778,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -37764,119 +37788,95 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.5% barrel, 16.5 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>47.52</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>96.5517</t>
+          <t>102.6127</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>0.1329</t>
+          <t>0.1969</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>30.28</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>0.1802</t>
-        </is>
-      </c>
-      <c r="BA138" t="inlineStr">
-        <is>
-          <t>10.47</t>
-        </is>
-      </c>
-      <c r="BB138" t="inlineStr">
-        <is>
-          <t>44.7</t>
-        </is>
-      </c>
-      <c r="BC138" t="inlineStr">
-        <is>
-          <t>90.18</t>
-        </is>
-      </c>
-      <c r="BD138" t="inlineStr">
-        <is>
-          <t>0.4237</t>
-        </is>
-      </c>
-      <c r="BE138" t="inlineStr">
-        <is>
-          <t>0.1831</t>
-        </is>
-      </c>
-      <c r="BF138" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
+          <t>0.2024</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr"/>
+      <c r="BB138" t="inlineStr"/>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
       <c r="BG138" t="inlineStr"/>
       <c r="BH138" t="inlineStr"/>
       <c r="BI138" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ138" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1604,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2164,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3288,7 +3284,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3354,34 +3350,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3572,7 +3564,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4412,7 +4404,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4478,34 +4470,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5256,7 +5244,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5816,7 +5804,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6660,7 +6648,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -9180,7 +9168,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9246,34 +9234,30 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10280,7 +10264,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10346,34 +10330,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11684,7 +11664,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12248,7 +12228,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12812,7 +12792,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13372,7 +13352,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13652,7 +13632,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -17292,7 +17272,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -18416,7 +18396,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -19536,7 +19516,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -21752,7 +21732,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -21816,28 +21796,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22588,7 +22572,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -22654,34 +22638,30 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22872,7 +22852,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -22938,34 +22918,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23156,7 +23132,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23972,7 +23948,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24812,7 +24788,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -25912,7 +25888,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -26196,7 +26172,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -28924,7 +28900,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29768,7 +29744,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -31424,7 +31400,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -32264,7 +32240,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -38916,7 +38892,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -39476,7 +39452,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -44468,7 +44444,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -44534,34 +44510,30 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47736,7 +47708,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -51118,7 +51090,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -51184,34 +51156,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -51962,7 +51930,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -52242,7 +52210,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -52522,7 +52490,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -53646,7 +53614,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -53712,34 +53680,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -53930,7 +53894,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -54770,7 +54734,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -54836,34 +54800,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -55614,7 +55574,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -56174,7 +56134,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>47.5</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6615,56 +6615,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>608369</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-19T22:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>669461</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6682,22 +6682,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>42.8</v>
+        <v>61.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>51.8</v>
+        <v>32.7</v>
       </c>
       <c r="R23" t="n">
-        <v>59.8</v>
+        <v>42.1</v>
       </c>
       <c r="S23" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>39.5</v>
+        <v>48.3</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6779,112 +6779,112 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>49.26</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>89.22</t>
+          <t>91.92</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>100.3066</t>
+          <t>102.637</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.3797</t>
+          <t>0.4892</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1827</t>
+          <t>0.2406</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.3573</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>72.01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.2343</t>
+          <t>0.1964</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.4461</t>
+          <t>0.3818</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>28.38</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6895,52 +6895,52 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>608369</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T22:40:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>669461</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -6962,22 +6962,22 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>61.3</v>
+        <v>42.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>32.7</v>
+        <v>51.8</v>
       </c>
       <c r="R24" t="n">
-        <v>41.1</v>
+        <v>59.8</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U24" t="n">
-        <v>48.3</v>
+        <v>39.5</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7059,112 +7059,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>91.92</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>102.637</t>
+          <t>100.3066</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.4892</t>
+          <t>0.3797</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.2406</t>
+          <t>0.1827</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3573</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>72.01</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1964</t>
+          <t>0.2343</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.3818</t>
+          <t>0.4461</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -12191,27 +12191,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>682928</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>CJ Abrams</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -12221,17 +12221,17 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>52.2</v>
+        <v>52.3</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12254,26 +12254,26 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P43" t="n">
         <v>39.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>49.2</v>
+        <v>47.5</v>
       </c>
       <c r="R43" t="n">
-        <v>38.1</v>
+        <v>42.1</v>
       </c>
       <c r="S43" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T43" t="n">
         <v>80</v>
       </c>
       <c r="U43" t="n">
-        <v>44.8</v>
+        <v>23.4</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -12330,22 +12330,22 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/26, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 19.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12355,112 +12355,112 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>10.51</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>101.0497</t>
+          <t>99.9352</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.3153</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>28.17</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>0.1586</t>
+          <t>0.2285</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12471,27 +12471,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>682928</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CJ Abrams</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12501,17 +12501,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12534,26 +12534,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P44" t="n">
         <v>39.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="R44" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S44" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T44" t="n">
         <v>80</v>
       </c>
       <c r="U44" t="n">
-        <v>23.4</v>
+        <v>44.8</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12610,22 +12610,22 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -12635,112 +12635,112 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>10.51</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>99.9352</t>
+          <t>101.0497</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.3153</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>28.17</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.2285</t>
+          <t>0.1586</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12751,24 +12751,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>665953</t>
+          <t>672284</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andrés Chaparro</t>
+          <t>Jarred Kelenic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>2026-08-20T00:05:00Z</t>
@@ -12781,17 +12781,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12800,7 +12800,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12814,26 +12814,26 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>47.9</v>
+        <v>59.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>47.5</v>
+        <v>32.7</v>
       </c>
       <c r="R45" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S45" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T45" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U45" t="n">
-        <v>37.8</v>
+        <v>38.3</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12885,27 +12885,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -12915,97 +12915,97 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>88.03</t>
+          <t>91.48</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>100.9561</t>
+          <t>101.7987</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.4328</t>
+          <t>0.4281</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2093</t>
+          <t>0.2083</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>43.07</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>27.61</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.2104</t>
+          <t>0.0903</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.3818</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
@@ -13031,24 +13031,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>672284</t>
+          <t>665953</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jarred Kelenic</t>
+          <t>Andrés Chaparro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>2026-08-20T00:05:00Z</t>
@@ -13061,17 +13061,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13080,7 +13080,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13094,26 +13094,26 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>59.9</v>
+        <v>47.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>32.7</v>
+        <v>47.5</v>
       </c>
       <c r="R46" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S46" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T46" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>38.3</v>
+        <v>37.8</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -13165,27 +13165,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -13195,97 +13195,97 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>91.48</t>
+          <t>88.03</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>101.7987</t>
+          <t>100.9561</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4281</t>
+          <t>0.4328</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.2083</t>
+          <t>0.2093</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>43.07</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0903</t>
+          <t>0.2104</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.3818</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
@@ -13871,27 +13871,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13901,17 +13901,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13920,7 +13920,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13938,22 +13938,22 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>37.9</v>
+        <v>49.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>49.2</v>
+        <v>32.7</v>
       </c>
       <c r="R49" t="n">
-        <v>38.1</v>
+        <v>42.1</v>
       </c>
       <c r="S49" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T49" t="n">
         <v>80</v>
       </c>
       <c r="U49" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14005,12 +14005,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -14020,72 +14020,72 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 19.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>43.97</t>
+          <t>51.04</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>90.68</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>100.4992</t>
+          <t>102.1802</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4318</t>
+          <t>0.4694</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1908</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3525</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>13.06</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>32.47</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -14095,52 +14095,52 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.3818</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>32.7</v>
       </c>
       <c r="R50" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S50" t="n">
         <v>93.2</v>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -14461,17 +14461,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14498,22 +14498,22 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>49.4</v>
+        <v>37.9</v>
       </c>
       <c r="Q51" t="n">
-        <v>32.7</v>
+        <v>49.2</v>
       </c>
       <c r="R51" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S51" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T51" t="n">
         <v>80</v>
       </c>
       <c r="U51" t="n">
-        <v>15.3</v>
+        <v>24.9</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14580,72 +14580,72 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>51.04</t>
+          <t>43.97</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>102.1802</t>
+          <t>100.4992</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.4694</t>
+          <t>0.4318</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.1908</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.3525</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -14655,52 +14655,52 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.3818</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -15831,27 +15831,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>677588</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>José Tena</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15861,17 +15861,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15894,26 +15894,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>39</v>
+        <v>33.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>42.3</v>
+        <v>47.5</v>
       </c>
       <c r="R56" t="n">
-        <v>38.1</v>
+        <v>42.1</v>
       </c>
       <c r="S56" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>73.2</v>
+        <v>27.6</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15965,27 +15965,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 2/11, 1 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.5% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15995,112 +15995,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>101.047</t>
+          <t>101.9048</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4149</t>
+          <t>0.3689</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1315</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3389</t>
+          <t>0.3027</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>72.94</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>23.82</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1824</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.3985</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16111,27 +16111,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>677588</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>José Tena</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -16141,17 +16141,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16174,26 +16174,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
       <c r="Q57" t="n">
-        <v>47.5</v>
+        <v>42.3</v>
       </c>
       <c r="R57" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S57" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T57" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>27.6</v>
+        <v>73.2</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -16245,27 +16245,27 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/11, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -16275,112 +16275,112 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>101.9048</t>
+          <t>101.047</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3689</t>
+          <t>0.4149</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1315</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3027</t>
+          <t>0.3389</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>72.94</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>33.56</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1824</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.3985</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -18887,27 +18887,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -18922,12 +18922,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Logan Gilbert</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>669302</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -18936,7 +18936,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18950,26 +18950,26 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>38.6</v>
+        <v>32.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>49.2</v>
+        <v>47.5</v>
       </c>
       <c r="R67" t="n">
-        <v>38.1</v>
+        <v>42.1</v>
       </c>
       <c r="S67" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T67" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U67" t="n">
-        <v>30.3</v>
+        <v>15.3</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -19021,27 +19021,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.7% barrel, 19.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -19051,112 +19051,112 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.55</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>101.5785</t>
+          <t>98.7911</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4273</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1593</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.1292</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr"/>
@@ -19167,27 +19167,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Logan Gilbert</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>669302</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -19230,26 +19230,26 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>32.5</v>
+        <v>38.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="R68" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S68" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T68" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U68" t="n">
-        <v>15.3</v>
+        <v>30.3</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19301,27 +19301,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.7% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -19331,112 +19331,112 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>88.55</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>98.7911</t>
+          <t>101.5785</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.4273</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.1593</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>35.18</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1292</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr"/>
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -23928,7 +23928,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>32.7</v>
       </c>
       <c r="R85" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S85" t="n">
         <v>96.59999999999999</v>
@@ -24143,7 +24143,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI85" t="inlineStr">
@@ -24720,7 +24720,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -29128,7 +29128,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -31624,7 +31624,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -32159,27 +32159,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-20T00:10:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -32194,12 +32194,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -32222,26 +32222,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>43.2</v>
+        <v>16.1</v>
       </c>
       <c r="Q115" t="n">
-        <v>14.3</v>
+        <v>46</v>
       </c>
       <c r="R115" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S115" t="n">
         <v>76.2</v>
       </c>
       <c r="T115" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U115" t="n">
-        <v>59.6</v>
+        <v>38.3</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
       <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -32293,27 +32293,27 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -32323,97 +32323,97 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>101.7303</t>
+          <t>97.6459</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1788</t>
+          <t>0.1073</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>53.63</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1619</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr">
@@ -32423,12 +32423,12 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32439,27 +32439,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-20T00:10:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -32474,12 +32474,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32488,7 +32488,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -32502,14 +32502,14 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>16.1</v>
+        <v>43.2</v>
       </c>
       <c r="Q116" t="n">
-        <v>46</v>
+        <v>14.3</v>
       </c>
       <c r="R116" t="n">
         <v>41.1</v>
@@ -32518,10 +32518,10 @@
         <v>76.2</v>
       </c>
       <c r="T116" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U116" t="n">
-        <v>38.3</v>
+        <v>59.6</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
       <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -32573,27 +32573,27 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32603,97 +32603,97 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>97.6459</t>
+          <t>101.7303</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1073</t>
+          <t>0.1788</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.2828</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>53.63</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t>0.1619</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr">
@@ -32708,7 +32708,7 @@
       </c>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -33280,7 +33280,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -34351,27 +34351,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>696285</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jacob Young</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-19T22:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -34381,17 +34381,17 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Max Scherzer</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>453286</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -34400,7 +34400,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -34414,26 +34414,26 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>15.3</v>
+        <v>18.5</v>
       </c>
       <c r="Q123" t="n">
-        <v>50.1</v>
+        <v>47.5</v>
       </c>
       <c r="R123" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S123" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T123" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U123" t="n">
-        <v>36.5</v>
+        <v>48.3</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -34490,122 +34490,122 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>32.97</t>
+          <t>33.36</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>97.0503</t>
+          <t>98.084</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>0.3702</t>
+          <t>0.378</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1132</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>34.86</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>0.1155</t>
+          <t>0.1239</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>35.82</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
-          <t>0.2013</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr">
@@ -34615,12 +34615,12 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI123" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ123" t="inlineStr"/>
@@ -34631,24 +34631,24 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>696285</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacob Young</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>WSH</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F124" t="inlineStr">
         <is>
           <t>2026-08-20T00:05:00Z</t>
@@ -34661,17 +34661,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -34680,7 +34680,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -34694,26 +34694,26 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>18.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q124" t="n">
-        <v>47.5</v>
+        <v>32.7</v>
       </c>
       <c r="R124" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S124" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T124" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U124" t="n">
-        <v>48.3</v>
+        <v>12</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -34765,7 +34765,7 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
@@ -34775,17 +34775,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -34795,97 +34795,97 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>33.36</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>98.084</t>
+          <t>98.6386</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>0.3348</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1132</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.2919</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>17.51</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.1239</t>
+          <t>0.1331</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.3818</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
@@ -34911,47 +34911,47 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T22:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Max Scherzer</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>453286</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -34978,22 +34978,22 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>21.7</v>
+        <v>15.3</v>
       </c>
       <c r="Q125" t="n">
-        <v>32.7</v>
+        <v>50.1</v>
       </c>
       <c r="R125" t="n">
         <v>41.1</v>
       </c>
       <c r="S125" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T125" t="n">
         <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>12</v>
+        <v>36.5</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -35045,12 +35045,12 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
@@ -35060,112 +35060,112 @@
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>32.97</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>98.6386</t>
+          <t>97.0503</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3348</t>
+          <t>0.3702</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.2919</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>68.77</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.1331</t>
+          <t>0.1155</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>10.58</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>35.82</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.3818</t>
+          <t>0.4498</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -36872,7 +36872,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -37407,27 +37407,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-20T00:10:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -37437,17 +37437,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -37470,26 +37470,26 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>40.4</v>
+        <v>19.7</v>
       </c>
       <c r="Q134" t="n">
-        <v>14.3</v>
+        <v>32.7</v>
       </c>
       <c r="R134" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S134" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T134" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -37524,7 +37524,7 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -37541,12 +37541,12 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -37556,12 +37556,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -37571,97 +37571,97 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>34.61</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>100.7878</t>
+          <t>98.7429</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.3707</t>
+          <t>0.3503</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.1146</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.2934</t>
+          <t>0.2841</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.1626</t>
+          <t>0.1376</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>40.96</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.3818</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1354</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr">
@@ -37671,12 +37671,12 @@
       </c>
       <c r="BH134" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -37687,27 +37687,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-20T00:10:00Z</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -37717,17 +37717,17 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -37736,7 +37736,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -37750,26 +37750,26 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P135" t="n">
-        <v>19.7</v>
+        <v>40.4</v>
       </c>
       <c r="Q135" t="n">
-        <v>32.7</v>
+        <v>14.3</v>
       </c>
       <c r="R135" t="n">
         <v>41.1</v>
       </c>
       <c r="S135" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T135" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U135" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -37804,7 +37804,7 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr"/>
@@ -37821,12 +37821,12 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -37836,12 +37836,12 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
@@ -37851,97 +37851,97 @@
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>98.7429</t>
+          <t>100.7878</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>0.3503</t>
+          <t>0.3707</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>0.1146</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>0.2841</t>
+          <t>0.2934</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>0.1376</t>
+          <t>0.1626</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>0.3818</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="BE135" t="inlineStr">
         <is>
-          <t>0.1354</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG135" t="inlineStr">
@@ -37956,7 +37956,7 @@
       </c>
       <c r="BI135" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ135" t="inlineStr"/>
@@ -38248,7 +38248,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -39368,7 +39368,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -39648,7 +39648,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -40488,7 +40488,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -40768,7 +40768,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -41023,56 +41023,56 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-19T22:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Cade Cavalli</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>676917</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -41086,26 +41086,26 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.5</v>
+        <v>27.2</v>
       </c>
       <c r="Q147" t="n">
-        <v>41.2</v>
+        <v>32.7</v>
       </c>
       <c r="R147" t="n">
-        <v>38.1</v>
+        <v>42.1</v>
       </c>
       <c r="S147" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T147" t="n">
         <v>50</v>
       </c>
       <c r="U147" t="n">
-        <v>24</v>
+        <v>5.7</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -41140,7 +41140,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -41157,12 +41157,12 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -41172,12 +41172,12 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -41187,88 +41187,112 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>84.45</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>92.5177</t>
+          <t>99.6925</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.3429</t>
+          <t>0.3529</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.0713</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.3191</t>
+          <t>0.2645</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.074</t>
-        </is>
-      </c>
-      <c r="BA147" t="inlineStr"/>
-      <c r="BB147" t="inlineStr"/>
-      <c r="BC147" t="inlineStr"/>
-      <c r="BD147" t="inlineStr"/>
-      <c r="BE147" t="inlineStr"/>
-      <c r="BF147" t="inlineStr"/>
+          <t>0.1487</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>6.46</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>40.96</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>88.68</t>
+        </is>
+      </c>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>0.3818</t>
+        </is>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>0.1354</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>21.75</t>
+        </is>
+      </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -41279,56 +41303,56 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T22:40:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Cade Cavalli</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>676917</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -41342,26 +41366,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>27.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q148" t="n">
-        <v>32.7</v>
+        <v>41.2</v>
       </c>
       <c r="R148" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S148" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T148" t="n">
         <v>50</v>
       </c>
       <c r="U148" t="n">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -41375,7 +41399,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -41396,7 +41420,7 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -41413,12 +41437,12 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -41428,12 +41452,12 @@
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.5% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -41443,112 +41467,88 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>84.45</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>99.6925</t>
+          <t>92.5177</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.3529</t>
+          <t>0.3429</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.0713</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.2645</t>
+          <t>0.3191</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.1487</t>
-        </is>
-      </c>
-      <c r="BA148" t="inlineStr">
-        <is>
-          <t>6.46</t>
-        </is>
-      </c>
-      <c r="BB148" t="inlineStr">
-        <is>
-          <t>40.96</t>
-        </is>
-      </c>
-      <c r="BC148" t="inlineStr">
-        <is>
-          <t>88.68</t>
-        </is>
-      </c>
-      <c r="BD148" t="inlineStr">
-        <is>
-          <t>0.3818</t>
-        </is>
-      </c>
-      <c r="BE148" t="inlineStr">
-        <is>
-          <t>0.1354</t>
-        </is>
-      </c>
-      <c r="BF148" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
-      </c>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr"/>
+      <c r="BB148" t="inlineStr"/>
+      <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="inlineStr"/>
+      <c r="BF148" t="inlineStr"/>
       <c r="BG148" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH148" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -41559,27 +41559,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -41589,26 +41589,26 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -41622,26 +41622,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>12.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q149" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="R149" t="n">
-        <v>47.2</v>
+        <v>42.1</v>
       </c>
       <c r="S149" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T149" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U149" t="n">
-        <v>28.9</v>
+        <v>27</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -41693,142 +41693,142 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 28.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>34.63</t>
+          <t>26.84</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>83.52</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>98.9375</t>
+          <t>95.205</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.3026</t>
+          <t>0.3205</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.0756</t>
+          <t>0.0785</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.2601</t>
+          <t>0.2989</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>69.53</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.1022</t>
+          <t>0.0855</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>0.4478</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE149" t="inlineStr">
         <is>
-          <t>0.1946</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH149" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -41839,27 +41839,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -41869,26 +41869,26 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>605488</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -41902,26 +41902,26 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>4.5</v>
+        <v>12.6</v>
       </c>
       <c r="Q150" t="n">
-        <v>47.5</v>
+        <v>48.1</v>
       </c>
       <c r="R150" t="n">
-        <v>41.1</v>
+        <v>47.2</v>
       </c>
       <c r="S150" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T150" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U150" t="n">
-        <v>27</v>
+        <v>28.9</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -41973,142 +41973,142 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 28.0 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>26.84</t>
+          <t>34.63</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>83.52</t>
+          <t>88.36</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>95.205</t>
+          <t>98.9375</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.3205</t>
+          <t>0.3026</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.0785</t>
+          <t>0.0756</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.2989</t>
+          <t>0.2601</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>14.32</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.0855</t>
+          <t>0.1022</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>36.18</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.4478</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1946</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH150" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -44032,7 +44032,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>46</v>
       </c>
       <c r="R158" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S158" t="n">
         <v>44.8</v>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="BH158" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI158" t="inlineStr">
@@ -44872,7 +44872,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -44896,7 +44896,7 @@
         <v>32.7</v>
       </c>
       <c r="R161" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S161" t="n">
         <v>44.8</v>
@@ -45087,7 +45087,7 @@
       </c>
       <c r="BH161" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI161" t="inlineStr">
@@ -46598,7 +46598,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>47.5</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -46813,7 +46813,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -50774,7 +50774,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>14.3</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>41.2</v>
       </c>
       <c r="R38" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S38" t="n">
         <v>94.90000000000001</v>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>41.2</v>
       </c>
       <c r="R51" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S51" t="n">
         <v>64.3</v>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
@@ -14736,7 +14736,7 @@
         <v>41.2</v>
       </c>
       <c r="R52" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S52" t="n">
         <v>86.40000000000001</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
@@ -16599,27 +16599,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-19T23:40:00Z</t>
+          <t>2026-08-20T00:10:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16629,17 +16629,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Ethan Pecko</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>814490</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16648,7 +16648,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16662,26 +16662,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>36.2</v>
+        <v>14</v>
       </c>
       <c r="Q59" t="n">
-        <v>55.5</v>
+        <v>41.2</v>
       </c>
       <c r="R59" t="n">
-        <v>47.2</v>
+        <v>41.6</v>
       </c>
       <c r="S59" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>5.7</v>
+        <v>40.7</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16716,7 +16716,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16733,12 +16733,12 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -16748,12 +16748,12 @@
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 19.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16763,112 +16763,88 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>100.9812</t>
+          <t>97.1398</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.3509</t>
+          <t>0.3887</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1106</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.2768</t>
+          <t>0.3326</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>74.01</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.1538</t>
-        </is>
-      </c>
-      <c r="BA59" t="inlineStr">
-        <is>
-          <t>9.21</t>
-        </is>
-      </c>
-      <c r="BB59" t="inlineStr">
-        <is>
-          <t>43.73</t>
-        </is>
-      </c>
-      <c r="BC59" t="inlineStr">
-        <is>
-          <t>90.21</t>
-        </is>
-      </c>
-      <c r="BD59" t="inlineStr">
-        <is>
-          <t>0.466</t>
-        </is>
-      </c>
-      <c r="BE59" t="inlineStr">
-        <is>
-          <t>0.1953</t>
-        </is>
-      </c>
-      <c r="BF59" t="inlineStr">
-        <is>
-          <t>29.81</t>
-        </is>
-      </c>
+          <t>0.1159</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr"/>
+      <c r="BB59" t="inlineStr"/>
+      <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -16879,27 +16855,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20T00:10:00Z</t>
+          <t>2026-08-19T23:40:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -16909,17 +16885,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Ethan Pecko</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>814490</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16942,26 +16918,26 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>14</v>
+        <v>36.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>41.2</v>
+        <v>55.5</v>
       </c>
       <c r="R60" t="n">
-        <v>41.1</v>
+        <v>47.2</v>
       </c>
       <c r="S60" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T60" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U60" t="n">
-        <v>40.7</v>
+        <v>5.7</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -16975,7 +16951,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -16996,7 +16972,7 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -17013,12 +16989,12 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -17028,12 +17004,12 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Contact streak: 9/23 over last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -17043,88 +17019,112 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>97.1398</t>
+          <t>100.9812</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.3887</t>
+          <t>0.3509</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.1106</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.3326</t>
+          <t>0.2768</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>74.01</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.1159</t>
-        </is>
-      </c>
-      <c r="BA60" t="inlineStr"/>
-      <c r="BB60" t="inlineStr"/>
-      <c r="BC60" t="inlineStr"/>
-      <c r="BD60" t="inlineStr"/>
-      <c r="BE60" t="inlineStr"/>
-      <c r="BF60" t="inlineStr"/>
+          <t>0.1538</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>9.21</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>43.73</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>90.21</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>0.466</t>
+        </is>
+      </c>
+      <c r="BE60" t="inlineStr">
+        <is>
+          <t>0.1953</t>
+        </is>
+      </c>
+      <c r="BF60" t="inlineStr">
+        <is>
+          <t>29.81</t>
+        </is>
+      </c>
       <c r="BG60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -18255,27 +18255,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20T00:05:00Z</t>
+          <t>2026-08-20T00:10:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18318,26 +18318,26 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>16.1</v>
+        <v>43.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>46</v>
+        <v>14.3</v>
       </c>
       <c r="R65" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S65" t="n">
         <v>76.2</v>
       </c>
       <c r="T65" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U65" t="n">
-        <v>38.3</v>
+        <v>59.6</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -18389,27 +18389,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -18419,97 +18419,97 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>97.6459</t>
+          <t>101.7303</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.3587</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.1073</t>
+          <t>0.1788</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.2828</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>53.63</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t>0.1619</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.4413</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
@@ -18519,12 +18519,12 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18535,27 +18535,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20T00:10:00Z</t>
+          <t>2026-08-20T00:05:00Z</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18598,26 +18598,26 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>43.2</v>
+        <v>16.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>14.3</v>
+        <v>46</v>
       </c>
       <c r="R66" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S66" t="n">
         <v>76.2</v>
       </c>
       <c r="T66" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U66" t="n">
-        <v>59.6</v>
+        <v>38.3</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr"/>
@@ -18669,27 +18669,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 14.5 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -18699,97 +18699,97 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>101.7303</t>
+          <t>97.6459</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.3587</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.1788</t>
+          <t>0.1073</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.2828</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>53.63</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1619</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.4413</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
@@ -18799,12 +18799,12 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -18864,7 +18864,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>41.2</v>
       </c>
       <c r="R67" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S67" t="n">
         <v>76.2</v>
@@ -19055,7 +19055,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>41.2</v>
       </c>
       <c r="R68" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S68" t="n">
         <v>93.2</v>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI68" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>14.3</v>
       </c>
       <c r="R73" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S73" t="n">
         <v>93.2</v>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
@@ -20776,7 +20776,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>14.3</v>
       </c>
       <c r="R74" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S74" t="n">
         <v>64.3</v>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
@@ -21287,24 +21287,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>LAA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>LAA</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>2026-08-20T00:10:00Z</t>
@@ -21322,12 +21322,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Ethan Pecko</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>814490</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21350,26 +21350,26 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>40.4</v>
+        <v>25</v>
       </c>
       <c r="Q76" t="n">
-        <v>14.3</v>
+        <v>41.2</v>
       </c>
       <c r="R76" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S76" t="n">
         <v>52.4</v>
       </c>
       <c r="T76" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
@@ -21436,12 +21436,12 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21451,99 +21451,75 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>100.7878</t>
+          <t>98.183</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.3707</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.2934</t>
+          <t>0.256</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>73.43</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1626</t>
-        </is>
-      </c>
-      <c r="BA76" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="BB76" t="inlineStr">
-        <is>
-          <t>33.6</t>
-        </is>
-      </c>
-      <c r="BC76" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="BD76" t="inlineStr">
-        <is>
-          <t>0.296</t>
-        </is>
-      </c>
-      <c r="BE76" t="inlineStr">
-        <is>
-          <t>0.097</t>
-        </is>
-      </c>
-      <c r="BF76" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
+          <t>0.1299</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr"/>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
       <c r="BG76" t="inlineStr">
         <is>
           <t>None</t>
@@ -21551,7 +21527,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
@@ -21567,24 +21543,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>694203</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>2026-08-20T00:10:00Z</t>
@@ -21602,12 +21578,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Ethan Pecko</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>814490</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21616,7 +21592,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21630,26 +21606,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>25</v>
+        <v>40.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>41.2</v>
+        <v>14.3</v>
       </c>
       <c r="R77" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S77" t="n">
         <v>52.4</v>
       </c>
       <c r="T77" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U77" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21684,7 +21660,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21701,7 +21677,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
@@ -21716,12 +21692,12 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21731,75 +21707,99 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>98.183</t>
+          <t>100.7878</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3707</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>0.2934</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>73.43</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1299</t>
-        </is>
-      </c>
-      <c r="BA77" t="inlineStr"/>
-      <c r="BB77" t="inlineStr"/>
-      <c r="BC77" t="inlineStr"/>
-      <c r="BD77" t="inlineStr"/>
-      <c r="BE77" t="inlineStr"/>
-      <c r="BF77" t="inlineStr"/>
+          <t>0.1626</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>33.6</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr">
+        <is>
+          <t>0.097</t>
+        </is>
+      </c>
+      <c r="BF77" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
       <c r="BG77" t="inlineStr">
         <is>
           <t>None</t>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
@@ -22432,7 +22432,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>14.3</v>
       </c>
       <c r="R80" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S80" t="n">
         <v>96.59999999999999</v>
@@ -22647,7 +22647,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
@@ -23832,7 +23832,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>41.2</v>
       </c>
       <c r="R85" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S85" t="n">
         <v>44.8</v>
@@ -24023,7 +24023,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI85" t="inlineStr">
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>14.3</v>
       </c>
       <c r="R86" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S86" t="n">
         <v>86.40000000000001</v>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
@@ -24672,7 +24672,7 @@
         <v>14.3</v>
       </c>
       <c r="R88" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S88" t="n">
         <v>94.90000000000001</v>
@@ -24863,7 +24863,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
@@ -25488,7 +25488,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>14.3</v>
       </c>
       <c r="R91" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S91" t="n">
         <v>44.8</v>
@@ -25703,7 +25703,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI91" t="inlineStr">
@@ -28334,7 +28334,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>14.3</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -28549,7 +28549,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -30014,7 +30014,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>41.2</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -30205,7 +30205,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
